--- a/hira_material_automation/output/monthly/202601_202606__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:54:17</t>
+          <t>2026-06-14T22:47:31</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>007ccef65412df1f5f5a4849a7b496aebfdc338a4e403158b99fceaaca813fe6</t>
+          <t>cdd4bd33a7352ee90e9ed7118d054d688ac71f4c5fd1c4ef9886a6cef8610d10</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:47:31</t>
+          <t>2026-06-24T22:52:18</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>cdd4bd33a7352ee90e9ed7118d054d688ac71f4c5fd1c4ef9886a6cef8610d10</t>
+          <t>1c35c3e2956705a941935ae9c6344dd267ce90be43036ea4074d9fd2dababe3d</t>
         </is>
       </c>
     </row>
